--- a/Inventory_trainingOutput.XLSX
+++ b/Inventory_trainingOutput.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Spectrum_sensing_base_on_Deep_learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB7E295-0D77-426D-9349-D490483CFF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D65D540-BEBF-43D2-96DE-1BE2009A5805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,9 +36,6 @@
     <t>Unetpp + AG + ASSP (1,2,3) + Gconv</t>
   </si>
   <si>
-    <t>96% (+_ 0.2%)</t>
-  </si>
-  <si>
     <t>Unetpp + AG + ASSP (3,6,9) + Gconv</t>
   </si>
   <si>
@@ -139,6 +136,9 @@
   </si>
   <si>
     <t>6.7M</t>
+  </si>
+  <si>
+    <t>96.50% (+_ 0.3%)</t>
   </si>
 </sst>
 </file>
@@ -231,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -243,10 +243,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -552,19 +548,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -572,94 +568,100 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1">
         <v>1E-3</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F2" s="1">
         <v>146</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="B3" s="1">
+        <v>12</v>
+      </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>1E-3</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" s="1">
         <v>146</v>
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="B4" s="1">
+        <v>12</v>
+      </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>1E-3</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" s="1">
         <v>151</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="B5" s="1">
+        <v>12</v>
+      </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>1E-3</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F5" s="1">
         <v>156</v>
       </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="B6" s="1">
+        <v>12</v>
+      </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>1E-3</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>35</v>
+      <c r="E6" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="F6" s="1">
         <v>191</v>
@@ -667,15 +669,17 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="B7" s="1">
+        <v>12</v>
+      </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>1E-3</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>26</v>
+      <c r="E7" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F7" s="1">
         <v>101</v>
@@ -683,53 +687,59 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>12</v>
+      </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>1E-3</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>27</v>
+      <c r="E8" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="F8" s="1">
         <v>101</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <v>12</v>
+      </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>1E-3</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F9" s="1">
         <v>59</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>12</v>
+      </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1">
         <v>1E-3</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1">
         <v>101</v>
@@ -737,15 +747,17 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>12</v>
+      </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1">
         <v>1E-3</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F11" s="1">
         <v>101</v>
@@ -753,15 +765,17 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>12</v>
+      </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1">
         <v>1E-3</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F12" s="1">
         <v>41</v>
@@ -769,15 +783,17 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>12</v>
+      </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
         <v>1E-3</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F13" s="1">
         <v>52</v>
@@ -785,15 +801,17 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="B14" s="1">
+        <v>12</v>
+      </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1">
         <v>1E-3</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F14" s="1">
         <v>101</v>
@@ -801,15 +819,17 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="B15" s="1">
+        <v>12</v>
+      </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1">
         <v>1E-3</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F15" s="1">
         <v>101</v>

--- a/Inventory_trainingOutput.XLSX
+++ b/Inventory_trainingOutput.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Spectrum_sensing_base_on_Deep_learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D65D540-BEBF-43D2-96DE-1BE2009A5805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588CAD86-E5C6-47A6-9BE6-01904A9EE792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="InventoryModel" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t>Model</t>
   </si>
@@ -136,9 +136,6 @@
   </si>
   <si>
     <t>6.7M</t>
-  </si>
-  <si>
-    <t>96.50% (+_ 0.3%)</t>
   </si>
 </sst>
 </file>
@@ -231,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -243,6 +240,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -570,8 +570,8 @@
       <c r="B2" s="1">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>37</v>
+      <c r="C2" s="9">
+        <v>0.96509999999999996</v>
       </c>
       <c r="D2" s="1">
         <v>1E-3</v>

--- a/Inventory_trainingOutput.XLSX
+++ b/Inventory_trainingOutput.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Spectrum_sensing_base_on_Deep_learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588CAD86-E5C6-47A6-9BE6-01904A9EE792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B300B4-0F07-4433-B0B1-83B2CB83222D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="InventoryModel" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
   <si>
     <t>Model</t>
   </si>
@@ -136,6 +136,12 @@
   </si>
   <si>
     <t>6.7M</t>
+  </si>
+  <si>
+    <t>Bad accuracy (not report)</t>
+  </si>
+  <si>
+    <t>Unetpp + AG + CASSP (1,2,3) (2,4,6)+ Gconv</t>
   </si>
 </sst>
 </file>
@@ -158,7 +164,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -186,6 +192,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -228,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -243,6 +255,8 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -528,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{017DAC86-C759-4C18-B683-28D08DD0B921}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.21875" customWidth="1"/>
@@ -537,7 +551,7 @@
     <col min="4" max="4" width="26.44140625" customWidth="1"/>
     <col min="5" max="5" width="20.44140625" customWidth="1"/>
     <col min="6" max="6" width="19.109375" customWidth="1"/>
-    <col min="9" max="9" width="15.109375" customWidth="1"/>
+    <col min="9" max="9" width="22.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -610,7 +624,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1">
@@ -632,7 +646,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1">
@@ -648,9 +662,13 @@
       <c r="F5" s="1">
         <v>156</v>
       </c>
+      <c r="H5" s="10"/>
+      <c r="I5" s="11" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="10" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="1">
@@ -669,7 +687,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B7" s="1">
         <v>12</v>
@@ -686,8 +704,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>8</v>
+      <c r="A8" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="B8" s="1">
         <v>12</v>
@@ -697,18 +715,15 @@
         <v>1E-3</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1">
         <v>101</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1">
         <v>12</v>
@@ -718,18 +733,18 @@
         <v>1E-3</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F9" s="1">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1">
         <v>12</v>
@@ -739,15 +754,18 @@
         <v>1E-3</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F10" s="1">
-        <v>101</v>
+        <v>59</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1">
         <v>12</v>
@@ -757,7 +775,7 @@
         <v>1E-3</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F11" s="1">
         <v>101</v>
@@ -765,7 +783,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1">
         <v>12</v>
@@ -775,15 +793,15 @@
         <v>1E-3</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F12" s="1">
-        <v>41</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1">
         <v>12</v>
@@ -793,15 +811,15 @@
         <v>1E-3</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F13" s="1">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>31</v>
+      <c r="A14" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="B14" s="1">
         <v>12</v>
@@ -811,15 +829,15 @@
         <v>1E-3</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F14" s="1">
-        <v>101</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" s="1">
         <v>12</v>
@@ -829,9 +847,27 @@
         <v>1E-3</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="1">
+        <v>12</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F16" s="1">
         <v>101</v>
       </c>
     </row>

--- a/Inventory_trainingOutput.XLSX
+++ b/Inventory_trainingOutput.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Spectrum_sensing_base_on_Deep_learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B300B4-0F07-4433-B0B1-83B2CB83222D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E90AF56-0EC4-4009-B664-70ECCB9643FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -240,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -256,7 +256,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -663,7 +662,7 @@
         <v>156</v>
       </c>
       <c r="H5" s="10"/>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -697,10 +696,10 @@
         <v>1E-3</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F7" s="1">
-        <v>101</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">

--- a/Inventory_trainingOutput.XLSX
+++ b/Inventory_trainingOutput.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Spectrum_sensing_base_on_Deep_learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E90AF56-0EC4-4009-B664-70ECCB9643FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F88192D-4AE6-46D6-BB2C-50F62D4D0D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -240,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -256,6 +256,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -724,17 +729,19 @@
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
-        <v>12</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1">
-        <v>1E-3</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="B9" s="5">
+        <v>12</v>
+      </c>
+      <c r="C9" s="12">
+        <v>0.97750000000000004</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="5">
         <v>101</v>
       </c>
       <c r="I9" s="8" t="s">
@@ -745,17 +752,19 @@
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
-        <v>12</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1">
-        <v>1E-3</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="B10" s="5">
+        <v>12</v>
+      </c>
+      <c r="C10" s="12">
+        <v>0.97899999999999998</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="5">
         <v>59</v>
       </c>
       <c r="I10" s="8" t="s">
@@ -766,17 +775,19 @@
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
-        <v>12</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1">
-        <v>1E-3</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="B11" s="5">
+        <v>12</v>
+      </c>
+      <c r="C11" s="12">
+        <v>0.97209999999999996</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="5">
         <v>101</v>
       </c>
     </row>
@@ -787,7 +798,7 @@
       <c r="B12" s="1">
         <v>12</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="11"/>
       <c r="D12" s="1">
         <v>1E-3</v>
       </c>

--- a/Inventory_trainingOutput.XLSX
+++ b/Inventory_trainingOutput.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Spectrum_sensing_base_on_Deep_learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F88192D-4AE6-46D6-BB2C-50F62D4D0D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C25B431-63F8-4201-90CE-4777CA2E3414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
   <si>
     <t>Model</t>
   </si>
@@ -84,12 +84,6 @@
     <t>Total parameters</t>
   </si>
   <si>
-    <t>Note: The number of features in group convolution is two times compare with traditional convolution</t>
-  </si>
-  <si>
-    <t>For example Conv(3x3x64) -&gt; Gconv(3x3x32x4)</t>
-  </si>
-  <si>
     <t>31.3M</t>
   </si>
   <si>
@@ -142,6 +136,18 @@
   </si>
   <si>
     <t>Unetpp + AG + CASSP (1,2,3) (2,4,6)+ Gconv</t>
+  </si>
+  <si>
+    <t>WiComNet 1</t>
+  </si>
+  <si>
+    <t>WiComNet 2</t>
+  </si>
+  <si>
+    <t>5M</t>
+  </si>
+  <si>
+    <t>7.8M</t>
   </si>
 </sst>
 </file>
@@ -164,7 +170,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -198,6 +204,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -240,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -259,6 +271,12 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -546,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{017DAC86-C759-4C18-B683-28D08DD0B921}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.21875" customWidth="1"/>
@@ -575,14 +593,14 @@
         <v>18</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1">
@@ -595,7 +613,7 @@
         <v>1E-3</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F2" s="1">
         <v>146</v>
@@ -605,8 +623,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1">
@@ -617,7 +635,7 @@
         <v>1E-3</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F3" s="1">
         <v>146</v>
@@ -627,8 +645,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1">
@@ -639,7 +657,7 @@
         <v>1E-3</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F4" s="1">
         <v>151</v>
@@ -649,8 +667,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1">
@@ -661,19 +679,19 @@
         <v>1E-3</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F5" s="1">
         <v>156</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>31</v>
       </c>
       <c r="B6" s="1">
         <v>12</v>
@@ -683,15 +701,15 @@
         <v>1E-3</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F6" s="1">
         <v>191</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>38</v>
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>36</v>
       </c>
       <c r="B7" s="1">
         <v>12</v>
@@ -701,15 +719,15 @@
         <v>1E-3</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F7" s="1">
         <v>151</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>24</v>
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>22</v>
       </c>
       <c r="B8" s="1">
         <v>12</v>
@@ -719,7 +737,7 @@
         <v>1E-3</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1">
         <v>101</v>
@@ -729,65 +747,61 @@
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="5">
-        <v>12</v>
-      </c>
-      <c r="C9" s="12">
+      <c r="B9" s="15">
+        <v>12</v>
+      </c>
+      <c r="C9" s="16">
         <v>0.97750000000000004</v>
       </c>
-      <c r="D9" s="5">
-        <v>1E-3</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="D9" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="15">
         <v>101</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>19</v>
-      </c>
+      <c r="I9" s="8"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="15">
         <v>12</v>
       </c>
       <c r="C10" s="12">
         <v>0.97899999999999998</v>
       </c>
-      <c r="D10" s="5">
-        <v>1E-3</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="5">
+      <c r="D10" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="15">
         <v>59</v>
       </c>
-      <c r="I10" s="8" t="s">
-        <v>20</v>
-      </c>
+      <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="5">
-        <v>12</v>
-      </c>
-      <c r="C11" s="12">
+      <c r="B11" s="15">
+        <v>12</v>
+      </c>
+      <c r="C11" s="16">
         <v>0.97209999999999996</v>
       </c>
-      <c r="D11" s="5">
-        <v>1E-3</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="5">
+      <c r="D11" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="15">
         <v>101</v>
       </c>
     </row>
@@ -803,7 +817,7 @@
         <v>1E-3</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F12" s="1">
         <v>101</v>
@@ -816,12 +830,14 @@
       <c r="B13" s="1">
         <v>12</v>
       </c>
-      <c r="C13" s="1"/>
+      <c r="C13" s="11">
+        <v>0.96760000000000002</v>
+      </c>
       <c r="D13" s="1">
         <v>1E-3</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F13" s="1">
         <v>41</v>
@@ -834,20 +850,22 @@
       <c r="B14" s="1">
         <v>12</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="11">
+        <v>0.96760000000000002</v>
+      </c>
       <c r="D14" s="1">
         <v>1E-3</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F14" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>31</v>
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="B15" s="1">
         <v>12</v>
@@ -857,15 +875,15 @@
         <v>1E-3</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F15" s="1">
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>32</v>
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="B16" s="1">
         <v>12</v>
@@ -875,10 +893,75 @@
         <v>1E-3</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F16" s="1">
         <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="1">
+        <v>12</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="1">
+        <v>12</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G21" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H22" s="4"/>
+      <c r="I22" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H23" s="7"/>
+      <c r="I23" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H24" s="5"/>
+      <c r="I24" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H25" s="10"/>
+      <c r="I25" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Inventory_trainingOutput.XLSX
+++ b/Inventory_trainingOutput.XLSX
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Spectrum_sensing_base_on_Deep_learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C25B431-63F8-4201-90CE-4777CA2E3414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD5A322-1E8E-45B1-A455-E17D0DB7AC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="InventoryModel" sheetId="2" r:id="rId1"/>
+    <sheet name="InventoryModel128" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
   <si>
     <t>Model</t>
   </si>
@@ -138,23 +138,29 @@
     <t>Unetpp + AG + CASSP (1,2,3) (2,4,6)+ Gconv</t>
   </si>
   <si>
-    <t>WiComNet 1</t>
-  </si>
-  <si>
-    <t>WiComNet 2</t>
-  </si>
-  <si>
     <t>5M</t>
   </si>
   <si>
     <t>7.8M</t>
+  </si>
+  <si>
+    <t>WiComNetA  (Base On Unet architecture)</t>
+  </si>
+  <si>
+    <t>WiComNetB  (Base On Unet architecture) + ASPP</t>
+  </si>
+  <si>
+    <t>DeepLabve (Vương)</t>
+  </si>
+  <si>
+    <t>20.6M</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,6 +171,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -252,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -270,15 +284,12 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -600,7 +611,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1">
@@ -624,7 +635,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1">
@@ -646,7 +657,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1">
@@ -668,7 +679,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1">
@@ -690,7 +701,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="13" t="s">
         <v>31</v>
       </c>
       <c r="B6" s="1">
@@ -708,7 +719,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="1">
@@ -726,7 +737,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="13" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="1">
@@ -747,19 +758,19 @@
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="15">
-        <v>12</v>
-      </c>
-      <c r="C9" s="16">
+      <c r="B9" s="1">
+        <v>12</v>
+      </c>
+      <c r="C9" s="11">
         <v>0.97750000000000004</v>
       </c>
-      <c r="D9" s="15">
-        <v>1E-3</v>
-      </c>
-      <c r="E9" s="17" t="s">
+      <c r="D9" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="1">
         <v>101</v>
       </c>
       <c r="I9" s="8"/>
@@ -768,19 +779,19 @@
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="1">
         <v>12</v>
       </c>
       <c r="C10" s="12">
         <v>0.97899999999999998</v>
       </c>
-      <c r="D10" s="15">
-        <v>1E-3</v>
-      </c>
-      <c r="E10" s="17" t="s">
+      <c r="D10" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="1">
         <v>59</v>
       </c>
       <c r="I10" s="8"/>
@@ -789,19 +800,19 @@
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="15">
-        <v>12</v>
-      </c>
-      <c r="C11" s="16">
+      <c r="B11" s="1">
+        <v>12</v>
+      </c>
+      <c r="C11" s="11">
         <v>0.97209999999999996</v>
       </c>
-      <c r="D11" s="15">
-        <v>1E-3</v>
-      </c>
-      <c r="E11" s="17" t="s">
+      <c r="D11" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="1">
         <v>101</v>
       </c>
     </row>
@@ -812,7 +823,9 @@
       <c r="B12" s="1">
         <v>12</v>
       </c>
-      <c r="C12" s="11"/>
+      <c r="C12" s="11">
+        <v>0.97130000000000005</v>
+      </c>
       <c r="D12" s="1">
         <v>1E-3</v>
       </c>
@@ -864,7 +877,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="13" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="1">
@@ -882,7 +895,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="13" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="1">
@@ -900,39 +913,61 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="1">
+        <v>12</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0.96850000000000003</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="E17" s="15" t="s">
         <v>37</v>
-      </c>
-      <c r="B17" s="1">
-        <v>12</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1">
-        <v>1E-3</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>39</v>
       </c>
       <c r="F17" s="1">
         <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="1">
+        <v>12</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0.97040000000000004</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="E18" s="15" t="s">
         <v>38</v>
-      </c>
-      <c r="B18" s="1">
-        <v>12</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1">
-        <v>1E-3</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F18" s="1">
         <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="1">
+        <v>12</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">

--- a/Inventory_trainingOutput.XLSX
+++ b/Inventory_trainingOutput.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Spectrum_sensing_base_on_Deep_learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD5A322-1E8E-45B1-A455-E17D0DB7AC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23645CF-8E1F-470E-A052-3F8ED97EA84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
   <si>
     <t>Model</t>
   </si>
@@ -150,10 +150,13 @@
     <t>WiComNetB  (Base On Unet architecture) + ASPP</t>
   </si>
   <si>
-    <t>DeepLabve (Vương)</t>
-  </si>
-  <si>
     <t>20.6M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ConvNet </t>
+  </si>
+  <si>
+    <t>DeepLabv3</t>
   </si>
 </sst>
 </file>
@@ -575,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{017DAC86-C759-4C18-B683-28D08DD0B921}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.21875" customWidth="1"/>
@@ -954,48 +957,68 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="1">
+        <v>12</v>
+      </c>
+      <c r="C19" s="11">
+        <v>0.4224</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B19" s="1">
-        <v>12</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1">
-        <v>1E-3</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F19" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G21" s="5" t="s">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="1">
+        <v>12</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G22" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H22" s="4"/>
-      <c r="I22" s="1" t="s">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H23" s="4"/>
+      <c r="I23" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H23" s="7"/>
-      <c r="I23" s="1" t="s">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H24" s="7"/>
+      <c r="I24" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H24" s="5"/>
-      <c r="I24" s="1" t="s">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H25" s="5"/>
+      <c r="I25" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H25" s="10"/>
-      <c r="I25" s="1" t="s">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H26" s="10"/>
+      <c r="I26" s="1" t="s">
         <v>35</v>
       </c>
     </row>

--- a/Inventory_trainingOutput.XLSX
+++ b/Inventory_trainingOutput.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Spectrum_sensing_base_on_Deep_learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23645CF-8E1F-470E-A052-3F8ED97EA84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBDB345-B9DD-4A5D-8AB1-793EE8C0B2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -982,7 +982,9 @@
       <c r="B20" s="1">
         <v>12</v>
       </c>
-      <c r="C20" s="1"/>
+      <c r="C20" s="11">
+        <v>0.42909999999999998</v>
+      </c>
       <c r="D20" s="1">
         <v>1E-3</v>
       </c>

--- a/Inventory_trainingOutput.XLSX
+++ b/Inventory_trainingOutput.XLSX
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Spectrum_sensing_base_on_Deep_learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBDB345-B9DD-4A5D-8AB1-793EE8C0B2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C609C79D-3E46-4569-988B-D22A8389B568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="InventoryModel128" sheetId="2" r:id="rId1"/>
+    <sheet name="SNR" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="56">
   <si>
     <t>Model</t>
   </si>
@@ -157,6 +158,42 @@
   </si>
   <si>
     <t>DeepLabv3</t>
+  </si>
+  <si>
+    <t>WiComNet</t>
+  </si>
+  <si>
+    <t>SNR</t>
+  </si>
+  <si>
+    <t>-5dB</t>
+  </si>
+  <si>
+    <t>0dB</t>
+  </si>
+  <si>
+    <t>5dB</t>
+  </si>
+  <si>
+    <t>10dB</t>
+  </si>
+  <si>
+    <t>15dB</t>
+  </si>
+  <si>
+    <t>20dB</t>
+  </si>
+  <si>
+    <t>25dB</t>
+  </si>
+  <si>
+    <t>30dB</t>
+  </si>
+  <si>
+    <t>ConvNet</t>
+  </si>
+  <si>
+    <t>Deeplabv3</t>
   </si>
 </sst>
 </file>
@@ -269,7 +306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -293,6 +330,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1028,4 +1067,249 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924A3231-A696-447E-8C96-A90CC7AA5E84}">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.36953000000000003</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.83025000000000004</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.95362999999999998</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.95735999999999999</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.96018999999999999</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.95920000000000005</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.95999000000000001</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.96421000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.64329999999999998</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.93323</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.97062000000000004</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.97421999999999997</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.97553999999999996</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.97577000000000003</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.97868999999999995</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.97736999999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.65793999999999997</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.93313000000000001</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.96877000000000002</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.97080999999999995</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.97409000000000001</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.97245999999999999</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.97521000000000002</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.97379000000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.65717999999999999</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.92530999999999997</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.96462000000000003</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.96643000000000001</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.97023999999999999</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.96694999999999998</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.97130000000000005</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.97211000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.61434999999999995</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.92859000000000003</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.96592</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.96989999999999998</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.97189000000000003</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.96974000000000005</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.97362000000000004</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.97280999999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.32923000000000002</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.37868000000000002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.40206999999999998</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.40214</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.40522999999999998</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.40584999999999999</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.40411000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0.23959</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.38916000000000001</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.44452000000000003</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.44480999999999998</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.44364999999999999</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.44564999999999999</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0.44389000000000001</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.44756000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>